--- a/out/MLP-mamba2_repeat_1_000005.xlsx
+++ b/out/MLP-mamba2_repeat_1_000005.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.599521431067185</v>
+        <v>1.002580650042519</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.199521431067184</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-1.204705233669806</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.199521431067184</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>2.199521431067184</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-1.204705233669806</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.599521431067185</v>
+        <v>1.002580650042519</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.199521431067184</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.199521431067184</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.199521431067184</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-1.204705233669806</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.199521431067184</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.599521431067185</v>
+        <v>1.002580650042519</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.331838802061187</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.204705233669806</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.599521431067185</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.199521431067184</v>
+        <v>1.002580650042519</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.199521431067184</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-1.204705233669806</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.331838802061187</v>
+        <v>1.002580650042519</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.199521431067184</v>
+        <v>1.002580650042519</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.199521431067184</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-1.204705233669806</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.199521431067184</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.599521431067185</v>
+        <v>1.002580650042519</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-1.204705233669806</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>2.199521431067184</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.7318388020611866</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-1.204705233669806</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44669,7 +44669,7 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.199521431067184</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-1.204705233669806</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46259,7 +46259,7 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>2.199521431067184</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47054,7 +47054,7 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47849,7 +47849,7 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.199521431067184</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.199521431067184</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-1.204705233669806</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.331838802061187</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.204705233669806</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.204705233669806</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58979,7 +58979,7 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59774,7 +59774,7 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>2.199521431067184</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60569,7 +60569,7 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-1.204705233669806</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>2.199521431067184</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7318388020611866</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62954,7 +62954,7 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-1.204705233669806</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.331838802061187</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.331838802061187</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65339,7 +65339,7 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>2.199521431067184</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66134,7 +66134,7 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-1.204705233669806</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.199521431067184</v>
+        <v>1.002580650042519</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.7318388020611866</v>
+        <v>1.002580650042519</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.199521431067184</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7318388020611866</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70109,7 +70109,7 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>2.199521431067184</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.199521431067184</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.7318388020611866</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.331838802061187</v>
+        <v>1.002580650042519</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.599521431067185</v>
+        <v>1.002580650042519</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>2.199521431067184</v>
+        <v>1.002580650042519</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>2.199521431067184</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-1.204705233669806</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7318388020611866</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79642,14 +79642,14 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.331838802061187</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80437,14 +80437,14 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.331838802061187</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.599521431067185</v>
+        <v>1.002580650042519</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82822,14 +82822,14 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.331838802061187</v>
+        <v>1.002580650042519</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>2.199521431067184</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>2.199521431067184</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85207,14 +85207,14 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7318388020611866</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86002,14 +86002,14 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7318388020611866</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86797,14 +86797,14 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.331838802061187</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88387,14 +88387,14 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.331838802061187</v>
+        <v>1.002580650042519</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89182,14 +89182,14 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.331838802061187</v>
+        <v>1.002580650042519</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89977,14 +89977,14 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.331838802061187</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.331838802061187</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.199521431067184</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>2.199521431067184</v>
+        <v>1.002580650042519</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93952,14 +93952,14 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.7318388020611866</v>
+        <v>1.002580650042519</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.199521431067184</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95542,14 +95542,14 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.7318388020611866</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>2.199521431067184</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>2.199521431067184</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>2.199521431067184</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>2.199521431067184</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>2.199521431067184</v>
+        <v>1.602580650042519</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.331838802061187</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101107,14 +101107,14 @@
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.599521431067185</v>
+        <v>-1.804705233669806</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/MLP-mamba2_repeat_1_000005.xlsx
+++ b/out/MLP-mamba2_repeat_1_000005.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.0775214109840431</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.599521431067185</v>
+        <v>0.5925037851595846</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595848</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.7925037851595846</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595846</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595846</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.1224785890159569</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.0775214109840431</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.07752141098404314</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.07752141098404314</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.0775214109840431</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595846</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595846</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.7925037851595848</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.199521431067184</v>
+        <v>0.122478589015957</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.331838802061187</v>
+        <v>0.122478589015957</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.0775214109840431</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.07752141098404305</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.07752141098404305</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.07752141098404303</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.0775214109840431</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-0.0775214109840431</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.1224785890159569</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595846</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595848</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.1224785890159569</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.0775214109840431</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.199521431067184</v>
+        <v>0.5925037851595846</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595846</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.7925037851595846</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.199521431067184</v>
+        <v>0.1224785890159569</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.1224785890159569</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.0775214109840431</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.0775214109840431</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.0775214109840431</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.0775214109840431</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>2.199521431067184</v>
+        <v>0.1224785890159569</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.1224785890159569</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.1224785890159569</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44669,7 +44669,7 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.199521431067184</v>
+        <v>0.1224785890159569</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.7925037851595846</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46259,7 +46259,7 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>2.199521431067184</v>
+        <v>0.122478589015957</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.7925037851595848</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47849,7 +47849,7 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595848</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595846</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.122478589015957</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.331838802061187</v>
+        <v>0.1224785890159571</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59774,7 +59774,7 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>2.199521431067184</v>
+        <v>0.122478589015957</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.7925037851595848</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>2.199521431067184</v>
+        <v>0.122478589015957</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.122478589015957</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62954,7 +62954,7 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-0.5475466071276708</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64544,7 +64544,7 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.07752141098404294</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.07752141098404294</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.7925037851595848</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.199521431067184</v>
+        <v>0.1224785890159571</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.7925037851595848</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.199521431067184</v>
+        <v>0.1224785890159571</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.7925037851595848</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70109,7 +70109,7 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595848</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595848</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.1224785890159572</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.0775214109840428</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.599521431067185</v>
+        <v>0.5925037851595849</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>2.199521431067184</v>
+        <v>0.792503785159585</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.1224785890159572</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.0775214109840428</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82027,14 +82027,14 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.07752141098404285</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82822,14 +82822,14 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.331838802061187</v>
+        <v>0.792503785159585</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>2.199521431067184</v>
+        <v>0.792503785159585</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>2.199521431067184</v>
+        <v>0.792503785159585</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85207,14 +85207,14 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.1224785890159572</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-0.5475466071276708</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.07752141098404289</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.199521431067184</v>
+        <v>0.1224785890159572</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92362,14 +92362,14 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.792503785159585</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>2.199521431067184</v>
+        <v>0.1224785890159571</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93952,14 +93952,14 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.7925037851595848</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.199521431067184</v>
+        <v>0.1224785890159571</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95542,14 +95542,14 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA119" t="n">
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.7925037851595848</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595848</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>2.199521431067184</v>
+        <v>0.792503785159585</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.331838802061187</v>
+        <v>0.7925037851595848</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.599521431067185</v>
+        <v>0.2574911870877711</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/MLP-mamba2_repeat_1_000005.xlsx
+++ b/out/MLP-mamba2_repeat_1_000005.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.3491031527519226</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.1600000000000003</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4806101024150848</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.0775214109840431</v>
+        <v>-0.1600000000000002</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.7109785676002502</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.5925037851595846</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.5476224422454834</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.7925037851595848</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.3754653632640839</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.7925037851595846</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.5762186050415039</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.7925037851595846</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.7554952502250671</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.7925037851595846</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.2257790714502335</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.1224785890159569</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.3666194677352905</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.2333690971136093</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.0775214109840431</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.5003147721290588</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.07752141098404314</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.2718698084354401</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.07752141098404314</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.3670612871646881</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.2866018712520599</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.2915924787521362</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.0775214109840431</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.7757756114006042</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.7925037851595846</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.6363852024078369</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.462528981303212</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.8309969305992126</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.7925037851595846</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.3588007390499115</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.7925037851595848</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.7786592841148376</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.122478589015957</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.203635185956955</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.122478589015957</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.1838527172803879</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.3142693042755127</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.0775214109840431</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.6828987002372742</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.07752141098404305</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4580685794353485</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.07752141098404305</v>
+        <v>-0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.3030644059181213</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.07752141098404303</v>
+        <v>-0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.6285299062728882</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.0775214109840431</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.3498604297637939</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.0775214109840431</v>
+        <v>0.16</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.4202023148536682</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.1224785890159569</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.5768371224403381</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.7925037851595846</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.8827130794525146</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.7925037851595848</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.2852940559387207</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.1224785890159569</v>
+        <v>0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.177890956401825</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>0.4617025852203369</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.3447480797767639</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.1545363515615463</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.0775214109840431</v>
+        <v>-0.3</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.6041995882987976</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.5925037851595846</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.5333542823791504</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.7925037851595846</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.2541980743408203</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.7925037851595846</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.5625206232070923</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.1224785890159569</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>0.3915646970272064</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.1224785890159569</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>0.4123036861419678</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>0.3538658022880554</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,10 +36716,10 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>0.3115330040454865</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.0775214109840431</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.500236988067627</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.0775214109840431</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>0.354405403137207</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.0775214109840431</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39101,10 +39101,10 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.4313279688358307</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39896,10 +39896,10 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.327709287405014</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.3093369603157043</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>0.3831765353679657</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.0775214109840431</v>
+        <v>0.16</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42281,10 +42281,10 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.604206383228302</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.1224785890159569</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43076,10 +43076,10 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>0.4643884003162384</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.1224785890159569</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43871,10 +43871,10 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.3275378048419952</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.1224785890159569</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44666,10 +44666,10 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.6038556694984436</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.1224785890159569</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45461,10 +45461,10 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.2660309374332428</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.7925037851595846</v>
+        <v>0.16</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46256,10 +46256,10 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.7339568138122559</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.122478589015957</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47051,10 +47051,10 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>0.2738882005214691</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.7925037851595848</v>
+        <v>0.3</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47846,10 +47846,10 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.5880208015441895</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.7925037851595848</v>
+        <v>0.3</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.5356085300445557</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.7925037851595846</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.2796694040298462</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.122478589015957</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50231,10 +50231,10 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.2649674117565155</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51026,10 +51026,10 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.3376589715480804</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51821,10 +51821,10 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.3891277015209198</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>0.3674125075340271</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53411,10 +53411,10 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.3731010258197784</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>0.4979463815689087</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.355112612247467</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.3336223959922791</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.4013812243938446</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.2652353942394257</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58181,10 +58181,10 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.1408650130033493</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58976,10 +58976,10 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.1732842475175858</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.1224785890159571</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59771,10 +59771,10 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.7630321383476257</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.122478589015957</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60566,10 +60566,10 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.1317076683044434</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.7925037851595848</v>
+        <v>0.16</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61361,10 +61361,10 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.7378062009811401</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.122478589015957</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.3144651055335999</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.122478589015957</v>
+        <v>0.16</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.4422658085823059</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.5475466071276708</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.3415124714374542</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.3</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.4515275061130524</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.07752141098404294</v>
+        <v>0.3</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.5244671106338501</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.07752141098404294</v>
+        <v>0.3</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.3366299569606781</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.7925037851595848</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.6790332198143005</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.1224785890159571</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.4018717706203461</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.7925037851595848</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.7769871950149536</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.1224785890159571</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.418637752532959</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.7925037851595848</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.7070835828781128</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.7925037851595848</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.7946114540100098</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.7925037851595848</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.496676504611969</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.1224785890159572</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.2648366689682007</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.3</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.2839628159999847</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.4934515953063965</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.3522364795207977</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.0775214109840428</v>
+        <v>-0.3</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.6557077169418335</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.5925037851595849</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.5767330527305603</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.462528981303212</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.7735955119132996</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.792503785159585</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.3659746646881104</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.1224785890159572</v>
+        <v>0.3</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.4413874745368958</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.16</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.4904380738735199</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.4739349484443665</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.3608859777450562</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.0775214109840428</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.7818552851676941</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.07752141098404285</v>
+        <v>-0.3</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.4172603189945221</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.792503785159585</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.5628098249435425</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.792503785159585</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.6805484890937805</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.792503785159585</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.3751358389854431</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.1224785890159572</v>
+        <v>0.16</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.3974064588546753</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.5475466071276708</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.4413065016269684</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.2839405834674835</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.4251859784126282</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.2802433371543884</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.3986667692661285</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.3777797222137451</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.07752141098404289</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.9313868284225464</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.1224785890159572</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.07288549840450287</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.792503785159585</v>
+        <v>0.16</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.9720324277877808</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.1224785890159571</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.275406688451767</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7925037851595848</v>
+        <v>0.16</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.8567600846290588</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.1224785890159571</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.4039944112300873</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7925037851595848</v>
+        <v>0.3</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.5406749248504639</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.7925037851595848</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.7361956238746643</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.462528981303212</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.9463163614273071</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.462528981303212</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.5707384943962097</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.462528981303212</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99521,10 +99521,10 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.894541323184967</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.792503785159585</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.01590319722890854</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.7925037851595848</v>
+        <v>-0.3700000000000003</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101107,14 +101107,14 @@
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.6635837554931641</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.2574911870877711</v>
+        <v>-0.5800000000000003</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/MLP-mamba2_repeat_1_000005.xlsx
+++ b/out/MLP-mamba2_repeat_1_000005.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.3491031527519226</v>
+        <v>0.349102795124054</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.1600000000000003</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.4806101024150848</v>
+        <v>0.4806101620197296</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.1600000000000002</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.7109785676002502</v>
+        <v>0.710978627204895</v>
       </c>
       <c r="JB4" t="n">
         <v>0.4399999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.3754653632640839</v>
+        <v>0.3754651248455048</v>
       </c>
       <c r="JB6" t="n">
         <v>0.7199999999999999</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.5762186050415039</v>
+        <v>0.5762183666229248</v>
       </c>
       <c r="JB7" t="n">
         <v>0.4399999999999999</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.7554952502250671</v>
+        <v>0.7554953098297119</v>
       </c>
       <c r="JB8" t="n">
         <v>0.1600000000000001</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.2257790714502335</v>
+        <v>0.2257789224386215</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.4399999999999999</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.3666194677352905</v>
+        <v>0.3666192591190338</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.5799999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.2333690971136093</v>
+        <v>0.233368918299675</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.8599999999999999</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.5003147721290588</v>
+        <v>0.5003145337104797</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.8599999999999999</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.2718698084354401</v>
+        <v>0.2718696594238281</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.8599999999999999</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.3670612871646881</v>
+        <v>0.3670610189437866</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.8599999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.2866018712520599</v>
+        <v>0.2866016030311584</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.7199999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.2915924787521362</v>
+        <v>0.2915922105312347</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.4399999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.1838527172803879</v>
+        <v>0.1838525533676147</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.4399999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.3142693042755127</v>
+        <v>0.3142691254615784</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.5799999999999998</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.6828987002372742</v>
+        <v>0.6828985810279846</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.5799999999999998</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.4580685794353485</v>
+        <v>0.4580683708190918</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.3</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.3030644059181213</v>
+        <v>0.303064227104187</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.3</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.6285299062728882</v>
+        <v>0.6285297274589539</v>
       </c>
       <c r="JB28" t="n">
         <v>0.02000000000000007</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.3498604297637939</v>
+        <v>0.349860280752182</v>
       </c>
       <c r="JB29" t="n">
         <v>0.16</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.4202023148536682</v>
+        <v>0.4202021062374115</v>
       </c>
       <c r="JB30" t="n">
         <v>0.4399999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.5768371224403381</v>
+        <v>0.5768369436264038</v>
       </c>
       <c r="JB31" t="n">
         <v>0.1600000000000001</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.2852940559387207</v>
+        <v>0.2852940261363983</v>
       </c>
       <c r="JB33" t="n">
         <v>0.3</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.4617025852203369</v>
+        <v>0.4617024064064026</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.8599999999999999</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.3447480797767639</v>
+        <v>0.3447479009628296</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.5799999999999998</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.1545363515615463</v>
+        <v>0.1545362174510956</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.3</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.6041995882987976</v>
+        <v>0.6041993498802185</v>
       </c>
       <c r="JB38" t="n">
         <v>0.1600000000000001</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.5333542823791504</v>
+        <v>0.5333540439605713</v>
       </c>
       <c r="JB39" t="n">
         <v>0.4399999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.2541980743408203</v>
+        <v>0.2541978657245636</v>
       </c>
       <c r="JB40" t="n">
         <v>0.4399999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.5625206232070923</v>
+        <v>0.5625203847885132</v>
       </c>
       <c r="JB41" t="n">
         <v>0.1600000000000001</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.3915646970272064</v>
+        <v>0.3915643990039825</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.1199999999999999</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.4123036861419678</v>
+        <v>0.4123034775257111</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.7199999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.3538658022880554</v>
+        <v>0.3538655638694763</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.8599999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.3115330040454865</v>
+        <v>0.311532735824585</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.8599999999999999</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.500236988067627</v>
+        <v>0.5002367496490479</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.7199999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.354405403137207</v>
+        <v>0.3544051945209503</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.7199999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.4313279688358307</v>
+        <v>0.4313277006149292</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.7199999999999999</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.327709287405014</v>
+        <v>0.3277090489864349</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.8599999999999999</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.3093369603157043</v>
+        <v>0.3093367516994476</v>
       </c>
       <c r="JB50" t="n">
         <v>0.02000000000000007</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.3831765353679657</v>
+        <v>0.3831762969493866</v>
       </c>
       <c r="JB51" t="n">
         <v>0.16</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.604206383228302</v>
+        <v>0.6042061448097229</v>
       </c>
       <c r="JB52" t="n">
         <v>0.1600000000000001</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.4643884003162384</v>
+        <v>0.4643881320953369</v>
       </c>
       <c r="JB53" t="n">
         <v>0.4399999999999999</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.3275378048419952</v>
+        <v>0.3275376260280609</v>
       </c>
       <c r="JB54" t="n">
         <v>0.4399999999999999</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.6038556694984436</v>
+        <v>0.6038553714752197</v>
       </c>
       <c r="JB55" t="n">
         <v>0.4399999999999999</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.2660309374332428</v>
+        <v>0.2660306990146637</v>
       </c>
       <c r="JB56" t="n">
         <v>0.16</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.7339568138122559</v>
+        <v>0.7339568734169006</v>
       </c>
       <c r="JB57" t="n">
         <v>0.4399999999999999</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.2738882005214691</v>
+        <v>0.2738880217075348</v>
       </c>
       <c r="JB58" t="n">
         <v>0.3</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.5880208015441895</v>
+        <v>0.5880205631256104</v>
       </c>
       <c r="JB59" t="n">
         <v>0.3</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.5356085300445557</v>
+        <v>0.5356082916259766</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.5799999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.2796694040298462</v>
+        <v>0.2796692848205566</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.5799999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.2649674117565155</v>
+        <v>0.2649672329425812</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.8599999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.3376589715480804</v>
+        <v>0.3376587629318237</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.3891277015209198</v>
+        <v>0.3891274631023407</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.9999999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.3674125075340271</v>
+        <v>0.3674122393131256</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.7199999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.3731010258197784</v>
+        <v>0.373100757598877</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.7199999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.4979463815689087</v>
+        <v>0.4979461431503296</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.7199999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.355112612247467</v>
+        <v>0.3551123738288879</v>
       </c>
       <c r="JB68" t="n">
         <v>0.02000000000000007</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.3336223959922791</v>
+        <v>0.3336222171783447</v>
       </c>
       <c r="JB69" t="n">
         <v>0.02000000000000007</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.4013812243938446</v>
+        <v>0.4013809859752655</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.2599999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.2652353942394257</v>
+        <v>0.2652351856231689</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.2599999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.1408650130033493</v>
+        <v>0.1408648788928986</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.5799999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.1732842475175858</v>
+        <v>0.173284038901329</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.1199999999999999</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.1317076683044434</v>
+        <v>0.1317076981067657</v>
       </c>
       <c r="JB75" t="n">
         <v>0.16</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.3144651055335999</v>
+        <v>0.3144651651382446</v>
       </c>
       <c r="JB77" t="n">
         <v>0.16</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.3415124714374542</v>
+        <v>0.341512531042099</v>
       </c>
       <c r="JB79" t="n">
         <v>0.3</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.3366299569606781</v>
+        <v>0.3366299867630005</v>
       </c>
       <c r="JB82" t="n">
         <v>0.4399999999999999</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.6790332198143005</v>
+        <v>0.6790331602096558</v>
       </c>
       <c r="JB83" t="n">
         <v>0.4399999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.7769871950149536</v>
+        <v>0.7769871354103088</v>
       </c>
       <c r="JB85" t="n">
         <v>0.7199999999999999</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.418637752532959</v>
+        <v>0.4186376631259918</v>
       </c>
       <c r="JB86" t="n">
         <v>0.7199999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.7070835828781128</v>
+        <v>0.707082986831665</v>
       </c>
       <c r="JB87" t="n">
         <v>0.8599999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.7946114540100098</v>
+        <v>0.7946115136146545</v>
       </c>
       <c r="JB88" t="n">
         <v>0.5799999999999998</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.496676504611969</v>
+        <v>0.4966762661933899</v>
       </c>
       <c r="JB89" t="n">
         <v>0.4399999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.2648366689682007</v>
+        <v>0.2648366987705231</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.3</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.2839628159999847</v>
+        <v>0.2839623093605042</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.5799999999999998</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.3522364795207977</v>
+        <v>0.3522357642650604</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.3</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.6557077169418335</v>
+        <v>0.6557072401046753</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.02000000000000007</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.3659746646881104</v>
+        <v>0.3659747242927551</v>
       </c>
       <c r="JB97" t="n">
         <v>0.3</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.4739349484443665</v>
+        <v>0.473934143781662</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.4399999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.3608859777450562</v>
+        <v>0.3608860373497009</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.4399999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.4172603189945221</v>
+        <v>0.4172602593898773</v>
       </c>
       <c r="JB103" t="n">
         <v>0.4399999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.6805484890937805</v>
+        <v>0.6805487871170044</v>
       </c>
       <c r="JB105" t="n">
         <v>0.1600000000000001</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.3751358389854431</v>
+        <v>0.3751357197761536</v>
       </c>
       <c r="JB106" t="n">
         <v>0.16</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.3974064588546753</v>
+        <v>0.3974057734012604</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.7199999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.4413065016269684</v>
+        <v>0.4413066804409027</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.9999999999999998</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.2839405834674835</v>
+        <v>0.2839397788047791</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.9999999999999998</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.4251859784126282</v>
+        <v>0.4251860976219177</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.9999999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.2802433371543884</v>
+        <v>0.2802426815032959</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.9999999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.3986667692661285</v>
+        <v>0.3986662030220032</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.7199999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.3777797222137451</v>
+        <v>0.3777791261672974</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.7199999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.275406688451767</v>
+        <v>0.2754067182540894</v>
       </c>
       <c r="JB117" t="n">
         <v>0.16</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.4039944112300873</v>
+        <v>0.4039944708347321</v>
       </c>
       <c r="JB119" t="n">
         <v>0.3</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.5406749248504639</v>
+        <v>0.5406741499900818</v>
       </c>
       <c r="JB120" t="n">
         <v>0.5799999999999998</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.7361956238746643</v>
+        <v>0.7361951470375061</v>
       </c>
       <c r="JB121" t="n">
         <v>0.4399999999999999</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.5707384943962097</v>
+        <v>0.5707383751869202</v>
       </c>
       <c r="JB123" t="n">
         <v>0.4399999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.01590319722890854</v>
+        <v>0.01590313017368317</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.3700000000000003</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.6635837554931641</v>
+        <v>0.6635833978652954</v>
       </c>
       <c r="JB126" t="n">
         <v>-0.5800000000000003</v>
